--- a/public/documentos/plantillas/fo-gf-003-relacion-pacientes.xlsx
+++ b/public/documentos/plantillas/fo-gf-003-relacion-pacientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ipspreventiva-my.sharepoint.com/personal/auxiliardecalidad_preventivaips_com_co/Documents/Escritorio/CONTABILIDAD/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{67D3D358-5717-C343-999C-8BDAEDD77A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3DBE6531-8C93-40AF-AE20-7935CCFF2789}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{67D3D358-5717-C343-999C-8BDAEDD77A0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E53CB7FA-6A4F-408F-B3A6-75A50D28B9F8}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="12360" yWindow="30" windowWidth="14400" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RELACIÓN DE PACIENTES" sheetId="1" r:id="rId1"/>
@@ -81,13 +81,13 @@
 RELACIÓN DE PACIENTES </t>
   </si>
   <si>
-    <t>Fecha: Diciembre de 2025</t>
-  </si>
-  <si>
     <t>Código: FO-GF-003</t>
   </si>
   <si>
     <t>Versión: 01</t>
+  </si>
+  <si>
+    <t>Fecha: Agosto de 2026</t>
   </si>
 </sst>
 </file>
@@ -1375,7 +1375,7 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
       <c r="K2" s="25" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="25.35" customHeight="1" x14ac:dyDescent="0.25">
@@ -1390,7 +1390,7 @@
       <c r="I3" s="28"/>
       <c r="J3" s="28"/>
       <c r="K3" s="25" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.25">
@@ -1405,7 +1405,7 @@
       <c r="I4" s="28"/>
       <c r="J4" s="28"/>
       <c r="K4" s="25" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="26.1" customHeight="1" x14ac:dyDescent="0.25">
